--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
@@ -490,26 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -520,26 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -550,26 +546,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -580,18 +572,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -606,22 +598,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -632,22 +628,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -658,22 +658,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -684,26 +688,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -714,26 +718,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1750,22 +1750,18 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -1876,18 +1872,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2406,22 +2406,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -2432,12 +2424,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F94" t="n">
         <v>3</v>
       </c>
@@ -2450,14 +2446,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2468,18 +2472,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -2508,22 +2516,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4220,18 +4220,14 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -4260,7 +4256,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4300,7 +4296,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4336,14 +4332,18 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -4426,14 +4426,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4480,14 +4480,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">

--- a/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-02-14_to_2025-02-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,26 +490,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Retail Sales MoMJAN</t>
+          <t>Retail Sales Ex Autos MoMJAN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -520,22 +520,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
+          <t>Import Prices MoMJAN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -546,22 +550,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Import Prices YoYJAN</t>
+          <t>Retail Sales Control Group MoMJAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.9%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +580,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Retail Sales YoYJAN</t>
+          <t>Export Prices MoMJAN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.2%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -598,26 +610,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Export Prices MoMJAN</t>
+          <t>Export Prices YoYJAN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.3%</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>2.7%</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -628,26 +636,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retail Sales Control Group MoMJAN</t>
+          <t>Import Prices YoYJAN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -658,26 +662,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Import Prices MoMJAN</t>
+          <t>Retail Sales Ex Gas/Autos MoMJAN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
+          <t>-0.5%</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -688,26 +688,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Retail Sales Ex Autos MoMJAN</t>
+          <t>Retail Sales MoMJAN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -718,18 +718,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Export Prices YoYJAN</t>
+          <t>Retail Sales YoYJAN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsFEB/14</t>
+          <t>MBA Mortgage Market IndexFEB/14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexFEB/14</t>
+          <t>MBA Purchase IndexFEB/14</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexFEB/14</t>
+          <t>MBA Mortgage Refinance IndexFEB/14</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexFEB/14</t>
+          <t>MBA Mortgage ApplicationsFEB/14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1750,18 +1750,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Building Permits MoM PrelJAN</t>
+          <t>Housing StartsJAN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1.39M</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>1.35M</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1872,22 +1876,18 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Housing StartsJAN</t>
+          <t>Building Permits MoM PrelJAN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1.39M</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.35M</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2388,12 +2388,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Philly Fed Business ConditionsFEB</t>
+          <t>Continuing Jobless ClaimsFEB/08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1879.0K</t>
+        </is>
+      </c>
       <c r="F92" t="n">
         <v>3</v>
       </c>
@@ -2406,14 +2410,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Philly Fed New OrdersFEB</t>
+          <t>Philadelphia Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -2424,18 +2436,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsFEB/08</t>
+          <t>Initial Jobless ClaimsFEB/15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>216K</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1879.0K</t>
+          <t>220.0K</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -2446,22 +2462,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Philadelphia Fed Manufacturing IndexFEB</t>
+          <t>Philly Fed New OrdersFEB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
@@ -2472,22 +2480,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsFEB/15</t>
+          <t>Philly Fed Prices PaidFEB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>216K</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>220.0K</t>
-        </is>
-      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Philly Fed Prices PaidFEB</t>
+          <t>Philly Fed EmploymentFEB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Philly Fed EmploymentFEB</t>
+          <t>Philly Fed Business ConditionsFEB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -4220,14 +4220,18 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
       <c r="F184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
@@ -4256,7 +4260,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>House Price Index YoYDEC</t>
+          <t>House Price Index MoMDEC</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4296,7 +4300,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>House Price Index MoMDEC</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMDEC</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4332,18 +4336,14 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYDEC</t>
+          <t>House Price Index YoYDEC</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>4.2%</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
@@ -4426,14 +4426,14 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CB Consumer ConfidenceFEB</t>
+          <t>Richmond Fed Services Revenues IndexFEB</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
+          <t>Richmond Fed Manufacturing IndexFEB</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Richmond Fed Manufacturing IndexFEB</t>
+          <t>Richmond Fed Manufacturing Shipments IndexFEB</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4480,14 +4480,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Richmond Fed Services Revenues IndexFEB</t>
+          <t>CB Consumer ConfidenceFEB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Money SupplyJAN</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>5-Year Note Auction</t>
+          <t>Money SupplyJAN</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4634,6 +4634,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-02-26 03:00:00+05:30</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>API Crude Oil Stock ChangeFEB/21</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
